--- a/data/trans_camb/P1001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 5,77</t>
+          <t>-5,1; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 11,67</t>
+          <t>0,61; 11,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; -3,78</t>
+          <t>-12,31; -3,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,97</t>
+          <t>2,8; 15,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 20,06</t>
+          <t>7,07; 20,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -4,01</t>
+          <t>-13,21; -3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 8,84</t>
+          <t>0,26; 8,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 14,62</t>
+          <t>5,6; 14,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -5,08</t>
+          <t>-11,04; -4,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 79,09</t>
+          <t>-41,07; 72,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 154,05</t>
+          <t>1,96; 159,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,08; -45,84</t>
+          <t>-90,72; -41,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 172,3</t>
+          <t>19,85; 180,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,34; 218,13</t>
+          <t>38,3; 222,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,08; -41,28</t>
+          <t>-82,88; -39,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 95,61</t>
+          <t>2,06; 88,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,14; 156,76</t>
+          <t>43,19; 154,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,24; -54,4</t>
+          <t>-82,61; -53,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,47</t>
+          <t>-4,13; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -2,49</t>
+          <t>-8,73; -2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,03</t>
+          <t>-4,4; 3,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 4,51</t>
+          <t>-4,28; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -1,47</t>
+          <t>-10,04; -1,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 0,19</t>
+          <t>-8,29; -0,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,06</t>
+          <t>-3,02; 2,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; -2,96</t>
+          <t>-8,34; -2,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,28</t>
+          <t>-5,18; 0,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 58,09</t>
+          <t>-40,82; 51,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,37; -35,15</t>
+          <t>-81,95; -39,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 46,5</t>
+          <t>-44,28; 54,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 35,69</t>
+          <t>-25,28; 36,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,73; -10,71</t>
+          <t>-57,06; -10,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 1,56</t>
+          <t>-45,53; 0,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 30,01</t>
+          <t>-23,15; 29,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,65; -28,55</t>
+          <t>-62,26; -28,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 3,26</t>
+          <t>-38,9; 3,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,07</t>
+          <t>0,1; 6,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,88</t>
+          <t>-2,67; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,62</t>
+          <t>-0,17; 5,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,44</t>
+          <t>3,52; 11,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,08</t>
+          <t>-1,14; 5,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,66</t>
+          <t>1,54; 7,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,74</t>
+          <t>2,66; 7,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,95</t>
+          <t>-1,16; 2,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,93</t>
+          <t>1,66; 5,88</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 552,36</t>
+          <t>-14,84; 488,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 185,01</t>
+          <t>-72,9; 190,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 495,4</t>
+          <t>-19,26; 450,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62,76; 504,01</t>
+          <t>59,74; 484,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 213,42</t>
+          <t>-25,55; 238,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,21; 325,63</t>
+          <t>21,0; 347,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,8; 361,3</t>
+          <t>62,64; 364,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 172,03</t>
+          <t>-28,92; 136,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,86; 294,27</t>
+          <t>34,49; 293,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,98</t>
+          <t>-0,18; 5,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,67</t>
+          <t>2,98; 10,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,63</t>
+          <t>0,38; 7,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,22; 18,18</t>
+          <t>8,86; 18,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,95</t>
+          <t>8,17; 18,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,49</t>
+          <t>-3,04; 6,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 11,75</t>
+          <t>5,53; 11,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,09</t>
+          <t>6,44; 12,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 5,55</t>
+          <t>-0,06; 5,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 419,34</t>
+          <t>-13,62; 393,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,76; 635,08</t>
+          <t>58,35; 634,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 409,6</t>
+          <t>-6,89; 453,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83,12; 307,86</t>
+          <t>82,93; 321,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,44; 310,48</t>
+          <t>80,57; 313,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 88,87</t>
+          <t>-33,72; 105,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,79; 294,16</t>
+          <t>81,75; 285,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>101,13; 318,41</t>
+          <t>92,82; 315,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 123,72</t>
+          <t>-1,13; 134,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,02</t>
+          <t>-6,38; 2,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 2,71</t>
+          <t>-6,21; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,03</t>
+          <t>-7,47; -0,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 17,63</t>
+          <t>5,17; 17,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,42</t>
+          <t>-4,88; 5,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 6,97</t>
+          <t>-1,91; 6,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,67</t>
+          <t>1,0; 8,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,16</t>
+          <t>-4,03; 2,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,34</t>
+          <t>-3,08; 2,78</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 72,34</t>
+          <t>-71,52; 64,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,83; 69,99</t>
+          <t>-69,82; 57,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,2; 22,2</t>
+          <t>-79,24; 8,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41,14; 377,07</t>
+          <t>48,34; 357,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 128,28</t>
+          <t>-49,12; 122,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 158,31</t>
+          <t>-22,12; 154,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,91; 172,17</t>
+          <t>10,89; 185,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 40,15</t>
+          <t>-48,26; 59,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 48,31</t>
+          <t>-35,32; 64,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,9</t>
+          <t>3,44; 10,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,67</t>
+          <t>2,63; 9,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,36</t>
+          <t>1,43; 6,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,52; 12,23</t>
+          <t>2,48; 11,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,78</t>
+          <t>5,14; 14,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,07</t>
+          <t>0,69; 7,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,52</t>
+          <t>4,26; 9,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,62; 11,08</t>
+          <t>4,61; 10,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,15</t>
+          <t>1,72; 6,35</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>107,69; 2129,17</t>
+          <t>82,48; 2380,2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>71,2; 1770,44</t>
+          <t>57,5; 1878,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49,25; 1486,92</t>
+          <t>37,92; 1664,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32,81; 430,55</t>
+          <t>34,02; 427,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58,58; 530,53</t>
+          <t>68,16; 538,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 261,22</t>
+          <t>9,18; 291,17</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>82,3; 474,36</t>
+          <t>93,83; 505,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>98,65; 529,18</t>
+          <t>107,13; 538,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41,85; 306,6</t>
+          <t>38,15; 323,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,11</t>
+          <t>-3,31; 1,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,84</t>
+          <t>-1,78; 3,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,75</t>
+          <t>0,13; 6,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,88</t>
+          <t>-5,57; 0,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,94</t>
+          <t>-1,02; 6,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,03</t>
+          <t>-5,98; 6,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,4</t>
+          <t>-3,62; 0,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,97</t>
+          <t>-0,56; 4,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,93</t>
+          <t>-1,76; 5,2</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 50,99</t>
+          <t>-46,45; 47,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 88,69</t>
+          <t>-25,1; 80,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 144,2</t>
+          <t>1,58; 146,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 11,89</t>
+          <t>-47,09; 7,51</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 66,79</t>
+          <t>-9,17; 70,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 63,24</t>
+          <t>-48,37; 61,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 6,44</t>
+          <t>-38,22; 8,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 55,07</t>
+          <t>-5,87; 58,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 67,86</t>
+          <t>-17,92; 70,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,63</t>
+          <t>-2,5; 3,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,61</t>
+          <t>-6,42; -1,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -1,24</t>
+          <t>-7,29; -1,14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,94</t>
+          <t>3,31; 10,26</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,32</t>
+          <t>-4,53; 1,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,68</t>
+          <t>3,38; 9,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,14</t>
+          <t>1,21; 6,14</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,79</t>
+          <t>-4,94; -0,96</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,93</t>
+          <t>-3,43; 3,26</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 53,75</t>
+          <t>-25,66; 50,91</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,25; -22,11</t>
+          <t>-67,3; -25,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-79,82; -17,46</t>
+          <t>-76,16; -17,46</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27,24; 123,91</t>
+          <t>29,08; 125,03</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 15,42</t>
+          <t>-40,71; 19,28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,81; 122,08</t>
+          <t>29,88; 124,84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,69; 78,0</t>
+          <t>11,51; 77,63</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-46,78; -9,88</t>
+          <t>-47,47; -9,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 35,6</t>
+          <t>-34,55; 37,93</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,44</t>
+          <t>-0,15; 2,3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,14</t>
+          <t>-1,08; 1,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,98</t>
+          <t>-1,89; 0,96</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,87</t>
+          <t>3,75; 6,91</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,28</t>
+          <t>1,32; 4,35</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,87</t>
+          <t>-0,79; 3,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,23</t>
+          <t>2,18; 4,23</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,53; 2,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,68</t>
+          <t>-0,68; 1,74</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 44,46</t>
+          <t>-2,56; 41,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 21,42</t>
+          <t>-15,92; 20,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 17,42</t>
+          <t>-29,18; 17,48</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>37,5; 79,08</t>
+          <t>37,03; 80,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,65; 49,13</t>
+          <t>13,1; 51,36</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,27</t>
+          <t>-8,1; 33,81</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,84; 57,87</t>
+          <t>26,56; 57,2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,11; 33,39</t>
+          <t>6,18; 33,07</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 22,98</t>
+          <t>-8,36; 23,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1001-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1001-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>-8,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,44</t>
+          <t>-8,61</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-8,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 5,19</t>
+          <t>-5,01; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 11,81</t>
+          <t>0,1; 11,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -3,71</t>
+          <t>-12,6; -4,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,96</t>
+          <t>2,7; 16,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 20,72</t>
+          <t>6,7; 20,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,72</t>
+          <t>-13,46; -4,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 8,14</t>
+          <t>0,37; 8,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,09</t>
+          <t>5,65; 14,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -4,97</t>
+          <t>-11,67; -5,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-75,39%</t>
+          <t>-78,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-70,0%</t>
+          <t>-71,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-72,6%</t>
+          <t>-74,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 72,52</t>
+          <t>-39,49; 66,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 159,96</t>
+          <t>-0,66; 150,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,72; -41,22</t>
+          <t>-92,6; -55,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 180,73</t>
+          <t>15,81; 170,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,3; 222,54</t>
+          <t>42,11; 229,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,88; -39,74</t>
+          <t>-84,14; -46,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 88,42</t>
+          <t>0,69; 91,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,19; 154,23</t>
+          <t>42,61; 151,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-82,61; -53,12</t>
+          <t>-84,15; -61,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,15</t>
+          <t>-4,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-2,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,29</t>
+          <t>-4,22; 3,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -2,67</t>
+          <t>-8,59; -2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,34</t>
+          <t>-4,56; 2,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 4,8</t>
+          <t>-4,46; 4,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -1,36</t>
+          <t>-9,86; -1,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; -0,05</t>
+          <t>-8,64; -0,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,93</t>
+          <t>-3,08; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -2,86</t>
+          <t>-8,25; -2,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,3</t>
+          <t>-5,19; 0,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,25%</t>
+          <t>-7,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,51%</t>
+          <t>-28,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,63%</t>
+          <t>-21,24%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 51,51</t>
+          <t>-40,66; 52,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,95; -39,75</t>
+          <t>-81,54; -38,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 54,15</t>
+          <t>-42,44; 46,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 36,88</t>
+          <t>-26,24; 38,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,06; -10,25</t>
+          <t>-57,83; -9,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 0,83</t>
+          <t>-48,49; -4,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 29,17</t>
+          <t>-22,88; 27,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,26; -28,22</t>
+          <t>-62,25; -26,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 3,12</t>
+          <t>-39,36; 2,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>4,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,31</t>
+          <t>-0,03; 6,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,92</t>
+          <t>-2,61; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,27</t>
+          <t>0,08; 5,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,35</t>
+          <t>3,38; 11,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,07</t>
+          <t>-1,41; 5,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,82</t>
+          <t>1,79; 8,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,7</t>
+          <t>2,75; 7,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,89</t>
+          <t>-1,22; 2,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,88</t>
+          <t>2,06; 6,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114,79%</t>
+          <t>131,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>125,08%</t>
+          <t>133,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>122,42%</t>
+          <t>134,24%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 488,87</t>
+          <t>-9,3; 563,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,9; 190,41</t>
+          <t>-73,25; 200,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 450,74</t>
+          <t>-8,31; 525,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59,74; 484,23</t>
+          <t>49,09; 467,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 238,89</t>
+          <t>-32,56; 228,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,0; 347,94</t>
+          <t>28,6; 376,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,64; 364,4</t>
+          <t>68,27; 375,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 136,19</t>
+          <t>-33,66; 136,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,49; 293,57</t>
+          <t>46,25; 301,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>3,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,94</t>
+          <t>0,09; 5,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,01</t>
+          <t>3,09; 10,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,12</t>
+          <t>-0,05; 6,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,68</t>
+          <t>9,1; 18,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 18,4</t>
+          <t>8,45; 18,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,31</t>
+          <t>0,08; 8,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,64</t>
+          <t>5,45; 11,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,86</t>
+          <t>6,66; 13,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,72</t>
+          <t>1,21; 6,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123,67%</t>
+          <t>112,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 393,13</t>
+          <t>-6,09; 402,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,35; 634,11</t>
+          <t>58,29; 674,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 453,21</t>
+          <t>-12,68; 412,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,93; 321,43</t>
+          <t>92,31; 332,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>80,57; 313,05</t>
+          <t>84,4; 329,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 105,24</t>
+          <t>-0,6; 149,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,75; 285,91</t>
+          <t>83,03; 284,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92,82; 315,82</t>
+          <t>101,77; 324,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 134,55</t>
+          <t>17,98; 163,13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 2,44</t>
+          <t>-6,08; 2,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 2,15</t>
+          <t>-6,41; 2,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -0,03</t>
+          <t>-8,07; -0,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 17,32</t>
+          <t>4,61; 17,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,48</t>
+          <t>-5,13; 5,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 6,81</t>
+          <t>-3,02; 5,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,9</t>
+          <t>0,99; 8,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,75</t>
+          <t>-4,36; 2,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,78</t>
+          <t>-3,86; 1,7</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-53,01%</t>
+          <t>-57,62%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-3,51%</t>
+          <t>-12,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 64,16</t>
+          <t>-69,64; 72,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-69,82; 57,2</t>
+          <t>-69,88; 55,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 8,01</t>
+          <t>-82,04; -1,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48,34; 357,84</t>
+          <t>41,34; 360,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 122,27</t>
+          <t>-51,62; 113,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 154,87</t>
+          <t>-30,17; 128,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,89; 185,03</t>
+          <t>7,6; 168,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 59,37</t>
+          <t>-47,32; 51,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 64,26</t>
+          <t>-42,68; 36,28</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>3,77</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,66</t>
+          <t>3,46; 11,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,57</t>
+          <t>2,8; 9,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,9</t>
+          <t>1,72; 6,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,4</t>
+          <t>2,45; 11,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,14; 14,8</t>
+          <t>4,22; 14,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,4</t>
+          <t>0,31; 6,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,8</t>
+          <t>4,04; 9,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,88</t>
+          <t>4,88; 11,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,35</t>
+          <t>1,79; 5,93</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>324,22%</t>
+          <t>315,1%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>139,39%</t>
+          <t>134,48%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>82,48; 2380,2</t>
+          <t>101,97; 2092,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>57,5; 1878,78</t>
+          <t>87,98; 2118,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37,92; 1664,38</t>
+          <t>48,31; 1361,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34,02; 427,41</t>
+          <t>29,45; 375,62</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68,16; 538,19</t>
+          <t>56,36; 505,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,18; 291,17</t>
+          <t>0,6; 234,22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>93,83; 505,03</t>
+          <t>99,39; 494,04</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>107,13; 538,81</t>
+          <t>116,82; 541,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38,15; 323,73</t>
+          <t>39,48; 316,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>3,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 1,92</t>
+          <t>-3,27; 1,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,63</t>
+          <t>-1,97; 3,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,71</t>
+          <t>0,14; 6,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,71</t>
+          <t>-5,57; 0,98</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 6,12</t>
+          <t>-1,18; 6,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 6,15</t>
+          <t>1,58; 8,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,55</t>
+          <t>-3,7; 0,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,06</t>
+          <t>-0,76; 3,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,2</t>
+          <t>1,73; 6,18</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 47,82</t>
+          <t>-46,36; 39,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 80,27</t>
+          <t>-31,54; 82,55</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,58; 146,29</t>
+          <t>0,48; 146,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,09; 7,51</t>
+          <t>-45,2; 11,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 70,02</t>
+          <t>-9,99; 69,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 61,83</t>
+          <t>12,44; 102,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 8,26</t>
+          <t>-40,05; 12,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 58,99</t>
+          <t>-7,68; 56,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 70,59</t>
+          <t>18,28; 86,43</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>1,8</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,54</t>
+          <t>-2,32; 3,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,77</t>
+          <t>-6,63; -1,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -1,14</t>
+          <t>-5,1; 0,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,26</t>
+          <t>2,79; 9,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,55</t>
+          <t>-4,81; 1,75</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,95</t>
+          <t>2,7; 8,55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,14</t>
+          <t>1,49; 6,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,96</t>
+          <t>-4,73; -0,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,26</t>
+          <t>-0,22; 3,81</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-46,83%</t>
+          <t>-29,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 50,91</t>
+          <t>-24,16; 51,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,3; -25,25</t>
+          <t>-67,48; -21,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-76,16; -17,46</t>
+          <t>-51,26; 2,76</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29,08; 125,03</t>
+          <t>23,97; 115,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 19,28</t>
+          <t>-42,63; 23,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,88; 124,84</t>
+          <t>22,9; 104,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,51; 77,63</t>
+          <t>15,01; 75,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-47,47; -9,7</t>
+          <t>-46,74; -11,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 37,93</t>
+          <t>-2,2; 49,39</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,3</t>
+          <t>-0,16; 2,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,14</t>
+          <t>-1,19; 1,11</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,96</t>
+          <t>-1,21; 1,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,91</t>
+          <t>3,6; 6,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,35</t>
+          <t>1,19; 4,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,0</t>
+          <t>0,89; 3,6</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,23</t>
+          <t>2,15; 4,22</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,42</t>
+          <t>0,49; 2,34</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,74</t>
+          <t>0,32; 2,24</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-4,9%</t>
+          <t>-0,26%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 41,44</t>
+          <t>-2,44; 44,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 20,12</t>
+          <t>-18,07; 21,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 17,48</t>
+          <t>-18,36; 21,34</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>37,03; 80,95</t>
+          <t>35,14; 75,35</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>13,1; 51,36</t>
+          <t>11,89; 51,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 33,81</t>
+          <t>8,65; 41,32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>26,56; 57,2</t>
+          <t>25,88; 58,26</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,18; 33,07</t>
+          <t>6,0; 32,22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 23,3</t>
+          <t>3,79; 31,43</t>
         </is>
       </c>
     </row>
